--- a/projects/ai-core/doc/data/res_syn_pe_area.xlsx
+++ b/projects/ai-core/doc/data/res_syn_pe_area.xlsx
@@ -20,9 +20,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="24">
-  <si>
-    <t xml:space="preserve">Intra-PE Cell Area — Baseline / Square / BFP / Square-BFP, ASAP7 RVT/TT (boundary-preserved synthesis)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="28">
+  <si>
+    <t xml:space="preserve">Intra-PE Cell Area — Baseline / Square / BFP / Square-BFP / Bit-Plane BFP, ASAP7 RVT/TT (boundary-preserved synthesis)</t>
   </si>
   <si>
     <t xml:space="preserve">#</t>
@@ -86,6 +86,15 @@
     <t xml:space="preserve">Square-BFP total </t>
   </si>
   <si>
+    <t xml:space="preserve">Bit-Plane BFP — pe_bpl_bfp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP8-Array (16 × dp_8_bpl_bfp)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bit-Plane BFP total </t>
+  </si>
+  <si>
     <t xml:space="preserve">Standalone dot-product cores — cross-check</t>
   </si>
   <si>
@@ -93,6 +102,9 @@
   </si>
   <si>
     <t xml:space="preserve">dp_8_sqr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dp_8_bpl_bfp</t>
   </si>
 </sst>
 </file>
@@ -231,7 +243,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -356,18 +368,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:H34"/>
-  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="B2:H42"/>
+  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="13.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="3.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="34.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="19.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="22.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="26.95"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="9" style="1" width="8.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="4" style="1" width="23.76"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="9" style="1" width="8.67"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -404,7 +412,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
@@ -415,7 +423,7 @@
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
     </row>
-    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="n">
         <v>1</v>
       </c>
@@ -438,7 +446,7 @@
         <v>0.700867755428711</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="n">
         <v>2</v>
       </c>
@@ -461,7 +469,7 @@
         <v>0.16140874022564</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="n">
         <v>3</v>
       </c>
@@ -484,7 +492,7 @@
         <v>0.0759519070668135</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="n">
         <v>4</v>
       </c>
@@ -507,7 +515,7 @@
         <v>0.0617715972788355</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="10" t="s">
         <v>13</v>
       </c>
@@ -524,8 +532,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="4" t="s">
         <v>14</v>
       </c>
@@ -536,7 +544,7 @@
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
     </row>
-    <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="n">
         <v>1</v>
       </c>
@@ -559,7 +567,7 @@
         <v>0.434627837118764</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="n">
         <v>2</v>
       </c>
@@ -582,7 +590,7 @@
         <v>0.159416198054748</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="n">
         <v>3</v>
       </c>
@@ -605,7 +613,7 @@
         <v>0.182910798744459</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="5" t="n">
         <v>4</v>
       </c>
@@ -628,7 +636,7 @@
         <v>0.0930274395745734</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="10" t="s">
         <v>16</v>
       </c>
@@ -645,8 +653,8 @@
         <v>0.869982043846762</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="4" t="s">
         <v>17</v>
       </c>
@@ -657,7 +665,7 @@
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
     </row>
-    <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="5" t="n">
         <v>1</v>
       </c>
@@ -680,7 +688,7 @@
         <v>0.723591909402849</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="5" t="n">
         <v>2</v>
       </c>
@@ -703,7 +711,7 @@
         <v>0.397497473376284</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="5" t="n">
         <v>3</v>
       </c>
@@ -726,7 +734,7 @@
         <v>0.201528116862422</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="5" t="n">
         <v>4</v>
       </c>
@@ -749,7 +757,7 @@
         <v>0.0781325311409524</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="10" t="s">
         <v>18</v>
       </c>
@@ -766,8 +774,8 @@
         <v>1.40075026483557</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="4" t="s">
         <v>19</v>
       </c>
@@ -778,7 +786,7 @@
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
     </row>
-    <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="5" t="n">
         <v>1</v>
       </c>
@@ -801,7 +809,7 @@
         <v>0.435704952025001</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="5" t="n">
         <v>2</v>
       </c>
@@ -824,7 +832,7 @@
         <v>0.632615814452055</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="5" t="n">
         <v>3</v>
       </c>
@@ -847,7 +855,7 @@
         <v>0.195417458363658</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="5" t="n">
         <v>4</v>
       </c>
@@ -870,7 +878,7 @@
         <v>0.100051626230261</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="10" t="s">
         <v>20</v>
       </c>
@@ -887,8 +895,8 @@
         <v>1.36378962085607</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="32" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="4" t="s">
         <v>21</v>
       </c>
@@ -899,7 +907,7 @@
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
     </row>
-    <row r="33" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="5" t="n">
         <v>1</v>
       </c>
@@ -907,42 +915,183 @@
         <v>22</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E33" s="8" t="n">
-        <v>202.414</v>
+        <v>181.5501875</v>
       </c>
       <c r="F33" s="8" t="n">
-        <v>202.414</v>
-      </c>
-      <c r="G33" s="5"/>
+        <v>2904.803</v>
+      </c>
+      <c r="G33" s="9" t="n">
+        <v>0.480682930461727</v>
+      </c>
       <c r="H33" s="8" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>0.665379872921005</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="5" t="n">
         <v>2</v>
       </c>
       <c r="C34" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="8" t="n">
+        <v>1874.828</v>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>1874.828</v>
+      </c>
+      <c r="G34" s="9" t="n">
+        <v>0.310244039665237</v>
+      </c>
+      <c r="H34" s="8" t="n">
+        <v>0.429451779135708</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>884.831</v>
+      </c>
+      <c r="F35" s="8" t="n">
+        <v>884.831</v>
+      </c>
+      <c r="G35" s="9" t="n">
+        <v>0.146420655047306</v>
+      </c>
+      <c r="H35" s="8" t="n">
+        <v>0.202681124446844</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="8" t="n">
+        <v>378.613</v>
+      </c>
+      <c r="F36" s="8" t="n">
+        <v>378.613</v>
+      </c>
+      <c r="G36" s="9" t="n">
+        <v>0.0626523748257303</v>
+      </c>
+      <c r="H36" s="8" t="n">
+        <v>0.0867258364254789</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D34" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" s="8" t="n">
+      <c r="C37" s="10"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10"/>
+      <c r="F37" s="11" t="n">
+        <v>6043.075</v>
+      </c>
+      <c r="G37" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="11" t="n">
+        <v>1.38423861292904</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
+    </row>
+    <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>202.414</v>
+      </c>
+      <c r="F40" s="8" t="n">
+        <v>202.414</v>
+      </c>
+      <c r="G40" s="5"/>
+      <c r="H40" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D41" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="8" t="n">
         <v>129.427</v>
       </c>
-      <c r="F34" s="8" t="n">
+      <c r="F41" s="8" t="n">
         <v>129.427</v>
       </c>
-      <c r="G34" s="5"/>
-      <c r="H34" s="8" t="n">
+      <c r="G41" s="5"/>
+      <c r="H41" s="8" t="n">
         <v>0.639417233985792</v>
       </c>
     </row>
+    <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>190.6335</v>
+      </c>
+      <c r="F42" s="8" t="n">
+        <v>190.6335</v>
+      </c>
+      <c r="G42" s="9"/>
+      <c r="H42" s="8" t="n">
+        <v>0.941799974310077</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="12">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B4:H4"/>
     <mergeCell ref="B9:E9"/>
@@ -953,6 +1102,8 @@
     <mergeCell ref="B25:H25"/>
     <mergeCell ref="B30:E30"/>
     <mergeCell ref="B32:H32"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B39:H39"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/projects/ai-core/doc/data/res_syn_pe_area.xlsx
+++ b/projects/ai-core/doc/data/res_syn_pe_area.xlsx
@@ -369,7 +369,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:H42"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="13.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="13.5" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="3.98"/>
@@ -412,7 +412,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
@@ -423,7 +423,7 @@
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
     </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="n">
         <v>1</v>
       </c>
@@ -446,7 +446,7 @@
         <v>0.700867755428711</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="n">
         <v>2</v>
       </c>
@@ -469,7 +469,7 @@
         <v>0.16140874022564</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="n">
         <v>3</v>
       </c>
@@ -492,7 +492,7 @@
         <v>0.0759519070668135</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="n">
         <v>4</v>
       </c>
@@ -515,7 +515,7 @@
         <v>0.0617715972788355</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="10" t="s">
         <v>13</v>
       </c>
@@ -532,8 +532,8 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="4" t="s">
         <v>14</v>
       </c>
@@ -544,7 +544,7 @@
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
     </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="n">
         <v>1</v>
       </c>
@@ -567,7 +567,7 @@
         <v>0.434627837118764</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="n">
         <v>2</v>
       </c>
@@ -590,7 +590,7 @@
         <v>0.159416198054748</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="n">
         <v>3</v>
       </c>
@@ -613,7 +613,7 @@
         <v>0.182910798744459</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="5" t="n">
         <v>4</v>
       </c>
@@ -636,7 +636,7 @@
         <v>0.0930274395745734</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="10" t="s">
         <v>16</v>
       </c>
@@ -653,8 +653,8 @@
         <v>0.869982043846762</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="18" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="4" t="s">
         <v>17</v>
       </c>
@@ -665,7 +665,7 @@
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
     </row>
-    <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="5" t="n">
         <v>1</v>
       </c>
@@ -688,7 +688,7 @@
         <v>0.723591909402849</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="5" t="n">
         <v>2</v>
       </c>
@@ -711,7 +711,7 @@
         <v>0.397497473376284</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="5" t="n">
         <v>3</v>
       </c>
@@ -734,7 +734,7 @@
         <v>0.201528116862422</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="5" t="n">
         <v>4</v>
       </c>
@@ -757,7 +757,7 @@
         <v>0.0781325311409524</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="10" t="s">
         <v>18</v>
       </c>
@@ -774,8 +774,8 @@
         <v>1.40075026483557</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="4" t="s">
         <v>19</v>
       </c>
@@ -786,7 +786,7 @@
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
     </row>
-    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="5" t="n">
         <v>1</v>
       </c>
@@ -809,7 +809,7 @@
         <v>0.435704952025001</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="5" t="n">
         <v>2</v>
       </c>
@@ -832,7 +832,7 @@
         <v>0.632615814452055</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="5" t="n">
         <v>3</v>
       </c>
@@ -855,7 +855,7 @@
         <v>0.195417458363658</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="5" t="n">
         <v>4</v>
       </c>
@@ -878,7 +878,7 @@
         <v>0.100051626230261</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="10" t="s">
         <v>20</v>
       </c>
@@ -895,8 +895,8 @@
         <v>1.36378962085607</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="32" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="4" t="s">
         <v>21</v>
       </c>
@@ -907,7 +907,7 @@
       <c r="G32" s="4"/>
       <c r="H32" s="4"/>
     </row>
-    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="5" t="n">
         <v>1</v>
       </c>
@@ -927,10 +927,10 @@
         <v>0.480682930461727</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>0.665379872921005</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>0.648493399165188</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="5" t="n">
         <v>2</v>
       </c>
@@ -950,10 +950,10 @@
         <v>0.310244039665237</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>0.429451779135708</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.418552852833762</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="5" t="n">
         <v>3</v>
       </c>
@@ -973,10 +973,10 @@
         <v>0.146420655047306</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>0.202681124446844</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.197537341732549</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="5" t="n">
         <v>4</v>
       </c>
@@ -996,10 +996,10 @@
         <v>0.0626523748257303</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>0.0867258364254789</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.0845248477566738</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="10" t="s">
         <v>23</v>
       </c>
@@ -1013,10 +1013,11 @@
         <v>1</v>
       </c>
       <c r="H37" s="11" t="n">
-        <v>1.38423861292904</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1.34910844148817</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="39" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="4" t="s">
         <v>24</v>
       </c>
@@ -1027,7 +1028,7 @@
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
     </row>
-    <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B40" s="5" t="n">
         <v>1</v>
       </c>
@@ -1048,7 +1049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="5" t="n">
         <v>2</v>
       </c>
@@ -1069,7 +1070,7 @@
         <v>0.639417233985792</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="17.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="5" t="n">
         <v>3</v>
       </c>
